--- a/feedback-reports/Full-Stack_Development_with_GenAI_Honours_Program.xlsx
+++ b/feedback-reports/Full-Stack_Development_with_GenAI_Honours_Program.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30023"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://niit.sharepoint.com/sites/NIIT-AIPoweredFSE/Shared Documents/General/Design Docs/FSE-v6/Website-Feedback/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nandita.vora\OneDrive - NIIT Limited\NIIT-AI Powered FSE - General\Design Docs\FSE-v6\Feedback-App\feedback-reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="298" documentId="11_71F05A531246E64FEE670415535DCE3AA7C4B014" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C207BE0-5BEB-4F80-91B2-80F921B41704}"/>
+  <xr:revisionPtr revIDLastSave="300" documentId="11_71F05A531246E64FEE670415535DCE3AA7C4B014" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BD311E8-C13C-4CAA-813A-050E3DB618DE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,10 +28,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="182">
   <si>
     <t>Program Name</t>
   </si>
@@ -137,6 +137,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Replace with:
 </t>
@@ -147,6 +148,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">• SQL Querying &amp; Data Operations
 </t>
@@ -156,6 +158,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Build strong hands-on skills to retrieve, analyze, and manipulate data using SQL, enabling you to extract meaningful insights and work effectively with real-world datasets.
 </t>
@@ -166,6 +169,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">• Database Design, Integrity &amp; Advanced Capabilities
 </t>
@@ -175,6 +179,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>Design structured databases using ER diagrams and define robust schemas while ensuring data consistency, and extend functionality through automation and support for modern data formats.</t>
     </r>
@@ -228,6 +233,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Replace with : 
@@ -239,6 +245,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Core Java Programming &amp; Problem Solving
@@ -249,6 +256,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Apply Core Java fundamentals—variables, control flow, arrays, strings, recursion, and searching/sorting—to build efficient, program logic.
@@ -260,6 +268,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Object-Oriented Application Development
@@ -270,6 +279,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Apply object-oriented concepts and exception handling to design well-structured Java applications.</t>
@@ -332,6 +342,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Replace with :
@@ -343,6 +354,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">• Data Structures Implementation
@@ -353,6 +365,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Implement core data structures such as arrays, stacks, queues, linked lists, trees, and hash tables along with searching and sorting algorithms.
@@ -364,6 +377,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">• Algorithm Analysis and Optimization
@@ -374,6 +388,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Analyse time and space complexity and apply recursion and suitable data structures to solve performance-critical problems.</t>
@@ -445,6 +460,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Replace with 
@@ -456,6 +472,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Testing and Collections
@@ -466,6 +483,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Write unit tests and manage data using collections and generics for organized, reliable programs.
@@ -477,6 +495,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Modern Java Practices
@@ -487,6 +506,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Apply functional programming features to write concise, efficient code for data processing.</t>
@@ -543,6 +563,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Replace with:
@@ -554,6 +575,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Responsive Web Design &amp; User Experience
@@ -564,6 +586,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Create visually appealing and responsive web interfaces by structuring content effectively and applying modern styling practices aligned with UI/UX principles.
@@ -575,6 +598,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">• Interactive Web Development &amp; API Integration
@@ -585,6 +609,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Build dynamic, interactive web applications by handling user interactions and seamlessly connecting front-end interfaces with backend services through APIs.</t>
@@ -636,6 +661,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Replace with below:
@@ -647,6 +673,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Component-Based UI Development
@@ -657,6 +684,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Build reusable and maintainable user interfaces using JSX, components, and props.
@@ -668,6 +696,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">State, Interactivity &amp; Data Handling
@@ -678,6 +707,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Create dynamic apps by managing state, handling interactions, and integrating APIs with React hooks.
@@ -689,6 +719,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">• Scalable, Styled &amp; Tested Apps
@@ -699,6 +730,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Improve reliability with TypeScript, design responsive UIs using Material UI, and ensure quality through testing using Jest and RTL.</t>
@@ -742,6 +774,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Replace with below content:
 </t>
@@ -752,6 +785,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">• Forms &amp; Navigation in React Applications
 </t>
@@ -761,6 +795,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Build and validate complex forms and enable seamless user journeys through efficient form handling and in-app routing.
 </t>
@@ -771,6 +806,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">• Authentication, State Management &amp; Performance
 </t>
@@ -780,6 +816,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>Implement secure access control and manage application state effectively using Context API while optimizing performance for production-ready apps.</t>
     </r>
@@ -819,6 +856,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">API Development and Testing
@@ -829,6 +867,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Design, build, and test RESTful APIs using Spring Boot with relational and NoSQL databases, including documentation and performance validation.
@@ -840,6 +879,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Scalability and Security
@@ -850,6 +890,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Enhance and secure services with pagination, filtering, microservices architecture, and authentication mechanisms.</t>
@@ -912,6 +953,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">LLM Application Development
@@ -922,6 +964,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Build LLM-powered applications using Spring AI with text generation, prompt design, and structured outputs.
@@ -933,6 +976,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Context-Aware AI Systems
@@ -943,6 +987,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Enhance applications with conversational memory and Retrieval-Augmented Generation (RAG) for context-driven experiences.</t>
@@ -1039,12 +1084,18 @@
   <si>
     <t>Replace with: 'Build and integrate AI features into full-stack web applications using Spring AI, including conversational memory and Retrieval-Augmented Generation (RAG).'</t>
   </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1057,6 +1108,7 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1068,22 +1120,26 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1091,6 +1147,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1112,6 +1169,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1129,8 +1187,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1154,8 +1224,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1178,12 +1254,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1223,6 +1310,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1532,18 +1628,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H63"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.9"/>
+  <dimension ref="A1:H62"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="19" style="2" customWidth="1"/>
-    <col min="2" max="2" width="83.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="83.6640625" style="2" customWidth="1"/>
     <col min="3" max="3" width="25" style="2" customWidth="1"/>
     <col min="4" max="4" width="45" style="2" customWidth="1"/>
     <col min="5" max="5" width="40" style="2" customWidth="1"/>
     <col min="6" max="6" width="45" style="2" customWidth="1"/>
-    <col min="7" max="7" width="46.5703125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="36.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="46.5546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="36.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" ht="24" customHeight="1">
@@ -1562,6 +1658,8 @@
       </c>
       <c r="E1" s="12"/>
       <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" s="10" customFormat="1" ht="30.75" customHeight="1">
       <c r="A2" s="9" t="s">
@@ -1574,6 +1672,8 @@
       <c r="D2" s="9"/>
       <c r="E2" s="12"/>
       <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
@@ -1594,8 +1694,14 @@
       <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="48">
+      <c r="G3" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="52.8">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -1612,10 +1718,10 @@
       <c r="F4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-    </row>
-    <row r="5" spans="1:8" ht="24">
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+    </row>
+    <row r="5" spans="1:8" ht="26.4">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -1633,7 +1739,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="48">
+    <row r="6" spans="1:8" ht="52.8">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -1653,7 +1759,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="24">
+    <row r="7" spans="1:8" ht="39.6">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -1673,7 +1779,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="154.5">
+    <row r="8" spans="1:8" ht="184.8">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -1691,7 +1797,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="12.75">
+    <row r="9" spans="1:8">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -1709,7 +1815,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="60">
+    <row r="10" spans="1:8" ht="66">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -1727,7 +1833,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="12.75">
+    <row r="11" spans="1:8">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -1745,7 +1851,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="24">
+    <row r="12" spans="1:8" ht="39.6">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -1765,7 +1871,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="121.5">
+    <row r="13" spans="1:8" ht="124.2">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -1783,7 +1889,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="12.75">
+    <row r="14" spans="1:8">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -1801,7 +1907,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="118.5">
+    <row r="15" spans="1:8" ht="132">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -1821,7 +1927,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="36">
+    <row r="16" spans="1:8" ht="39.6">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -1841,7 +1947,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="12.75">
+    <row r="17" spans="1:6">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -1859,7 +1965,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="12.75">
+    <row r="18" spans="1:6">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -1877,7 +1983,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="135">
+    <row r="19" spans="1:6" ht="138">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -1895,7 +2001,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="12.75">
+    <row r="20" spans="1:6">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -1913,7 +2019,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="24">
+    <row r="21" spans="1:6" ht="26.4">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -1933,7 +2039,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="72">
+    <row r="22" spans="1:6" ht="79.2">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -1953,7 +2059,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="36">
+    <row r="23" spans="1:6" ht="39.6">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -1973,7 +2079,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="12.75">
+    <row r="24" spans="1:6">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -1991,7 +2097,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="12.75">
+    <row r="25" spans="1:6">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -2009,7 +2115,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="108">
+    <row r="26" spans="1:6" ht="110.4">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -2027,7 +2133,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="12.75">
+    <row r="27" spans="1:6">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -2045,7 +2151,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="48">
+    <row r="28" spans="1:6" ht="52.8">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -2065,7 +2171,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="118.5">
+    <row r="29" spans="1:6" ht="132">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -2085,7 +2191,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="24">
+    <row r="30" spans="1:6" ht="26.4">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -2105,7 +2211,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="12.75">
+    <row r="31" spans="1:6">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -2123,7 +2229,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="121.5">
+    <row r="32" spans="1:6" ht="124.2">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -2141,7 +2247,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="12.75">
+    <row r="33" spans="1:8">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -2159,7 +2265,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="72">
+    <row r="34" spans="1:8" ht="79.2">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -2177,7 +2283,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="13.5">
+    <row r="35" spans="1:8" ht="27.6">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -2197,7 +2303,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="12.75">
+    <row r="36" spans="1:8">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -2215,7 +2321,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="13.5">
+    <row r="37" spans="1:8">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -2234,7 +2340,7 @@
       </c>
       <c r="H37" s="8"/>
     </row>
-    <row r="38" spans="1:8" ht="174.75">
+    <row r="38" spans="1:8" ht="179.4">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -2252,7 +2358,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="12.75">
+    <row r="39" spans="1:8">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -2270,7 +2376,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="72">
+    <row r="40" spans="1:8" ht="79.2">
       <c r="A40" s="3">
         <v>37</v>
       </c>
@@ -2288,7 +2394,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="12.75">
+    <row r="41" spans="1:8">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -2306,7 +2412,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="12.75">
+    <row r="42" spans="1:8">
       <c r="A42" s="3">
         <v>39</v>
       </c>
@@ -2324,7 +2430,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="118.5">
+    <row r="43" spans="1:8" ht="145.19999999999999">
       <c r="A43" s="3">
         <v>40</v>
       </c>
@@ -2342,7 +2448,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="12.75">
+    <row r="44" spans="1:8">
       <c r="A44" s="3">
         <v>41</v>
       </c>
@@ -2360,7 +2466,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="72">
+    <row r="45" spans="1:8" ht="79.2">
       <c r="A45" s="3">
         <v>42</v>
       </c>
@@ -2378,7 +2484,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="24">
+    <row r="46" spans="1:8" ht="26.4">
       <c r="A46" s="3">
         <v>43</v>
       </c>
@@ -2396,7 +2502,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="12.75">
+    <row r="47" spans="1:8">
       <c r="A47" s="3">
         <v>44</v>
       </c>
@@ -2414,7 +2520,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="135">
+    <row r="48" spans="1:8" ht="138">
       <c r="A48" s="3">
         <v>45</v>
       </c>
@@ -2432,7 +2538,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="12.75">
+    <row r="49" spans="1:7">
       <c r="A49" s="3">
         <v>46</v>
       </c>
@@ -2450,7 +2556,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="72">
+    <row r="50" spans="1:7" ht="79.2">
       <c r="A50" s="3">
         <v>47</v>
       </c>
@@ -2468,7 +2574,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="24">
+    <row r="51" spans="1:7" ht="26.4">
       <c r="A51" s="3">
         <v>48</v>
       </c>
@@ -2488,7 +2594,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="12.75">
+    <row r="52" spans="1:7">
       <c r="A52" s="3">
         <v>49</v>
       </c>
@@ -2506,7 +2612,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="12.75">
+    <row r="53" spans="1:7">
       <c r="A53" s="3">
         <v>50</v>
       </c>
@@ -2524,7 +2630,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="121.5">
+    <row r="54" spans="1:7" ht="138">
       <c r="A54" s="3">
         <v>51</v>
       </c>
@@ -2542,7 +2648,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="12.75">
+    <row r="55" spans="1:7">
       <c r="A55" s="3">
         <v>52</v>
       </c>
@@ -2560,7 +2666,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="84">
+    <row r="56" spans="1:7" ht="92.4">
       <c r="A56" s="3">
         <v>53</v>
       </c>
@@ -2578,7 +2684,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="60">
+    <row r="57" spans="1:7" ht="66">
       <c r="A57" s="3">
         <v>54</v>
       </c>
@@ -2598,7 +2704,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="48">
+    <row r="58" spans="1:7" ht="52.8">
       <c r="A58" s="3">
         <v>55</v>
       </c>
@@ -2616,7 +2722,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="24">
+    <row r="59" spans="1:7" ht="39.6">
       <c r="A59" s="3">
         <v>56</v>
       </c>
@@ -2636,7 +2742,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="36">
+    <row r="60" spans="1:7" ht="39.6">
       <c r="A60" s="3">
         <v>57</v>
       </c>
@@ -2654,7 +2760,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="142.5">
+    <row r="61" spans="1:7" ht="171.6">
       <c r="A61" s="3">
         <v>58</v>
       </c>
@@ -2675,7 +2781,7 @@
       </c>
       <c r="G61" s="6"/>
     </row>
-    <row r="62" spans="1:7" ht="48">
+    <row r="62" spans="1:7" ht="52.8">
       <c r="A62" s="3">
         <v>59</v>
       </c>
@@ -2695,9 +2801,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="12.75"/>
   </sheetData>
-  <autoFilter ref="A1:F62" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{7EC993AE-BD08-4FAE-B116-D47C25032B82}"/>
   </hyperlinks>
@@ -2706,12 +2810,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008081BF50E816F94B87E854E2907183B0" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1f6f57204d0cc9b1c65f7ab94eaa7dcc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8b8ad293-1655-4b1e-95cd-578b981aff66" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0ed196dee19b1527225c6137bc92e865" ns2:_="">
     <xsd:import namespace="8b8ad293-1655-4b1e-95cd-578b981aff66"/>
@@ -2873,6 +2971,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2883,13 +2987,43 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B34EA2C4-2285-4497-A663-7BC8A09FEAFD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A0A7D80-6346-4EAB-865F-2A3CADAA0676}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8b8ad293-1655-4b1e-95cd-578b981aff66"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A0A7D80-6346-4EAB-865F-2A3CADAA0676}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B34EA2C4-2285-4497-A663-7BC8A09FEAFD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8b8ad293-1655-4b1e-95cd-578b981aff66"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B384905-33E6-4B60-BC29-CDB45CE8B04B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B384905-33E6-4B60-BC29-CDB45CE8B04B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/feedback-reports/Full-Stack_Development_with_GenAI_Honours_Program.xlsx
+++ b/feedback-reports/Full-Stack_Development_with_GenAI_Honours_Program.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nandita.vora\OneDrive - NIIT Limited\NIIT-AI Powered FSE - General\Design Docs\FSE-v6\Feedback-App\feedback-reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="300" documentId="11_71F05A531246E64FEE670415535DCE3AA7C4B014" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BD311E8-C13C-4CAA-813A-050E3DB618DE}"/>
+  <xr:revisionPtr revIDLastSave="302" documentId="11_71F05A531246E64FEE670415535DCE3AA7C4B014" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{E88C2044-D968-4508-A85F-A5DA46ADCF1B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,23 +23,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="184">
   <si>
     <t>Program Name</t>
   </si>
@@ -1089,6 +1078,12 @@
   </si>
   <si>
     <t>Remarks</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>suggestion fixed</t>
   </si>
 </sst>
 </file>
@@ -2538,7 +2533,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:8">
       <c r="A49" s="3">
         <v>46</v>
       </c>
@@ -2556,7 +2551,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="79.2">
+    <row r="50" spans="1:8" ht="79.2">
       <c r="A50" s="3">
         <v>47</v>
       </c>
@@ -2574,7 +2569,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="26.4">
+    <row r="51" spans="1:8" ht="26.4">
       <c r="A51" s="3">
         <v>48</v>
       </c>
@@ -2594,7 +2589,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:8">
       <c r="A52" s="3">
         <v>49</v>
       </c>
@@ -2612,7 +2607,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:8">
       <c r="A53" s="3">
         <v>50</v>
       </c>
@@ -2630,7 +2625,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="138">
+    <row r="54" spans="1:8" ht="138">
       <c r="A54" s="3">
         <v>51</v>
       </c>
@@ -2648,7 +2643,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:8">
       <c r="A55" s="3">
         <v>52</v>
       </c>
@@ -2666,7 +2661,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="92.4">
+    <row r="56" spans="1:8" ht="92.4">
       <c r="A56" s="3">
         <v>53</v>
       </c>
@@ -2684,7 +2679,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="66">
+    <row r="57" spans="1:8" ht="66">
       <c r="A57" s="3">
         <v>54</v>
       </c>
@@ -2704,7 +2699,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="52.8">
+    <row r="58" spans="1:8" ht="52.8">
       <c r="A58" s="3">
         <v>55</v>
       </c>
@@ -2722,7 +2717,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="39.6">
+    <row r="59" spans="1:8" ht="39.6">
       <c r="A59" s="3">
         <v>56</v>
       </c>
@@ -2741,8 +2736,14 @@
       <c r="F59" s="3" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" ht="39.6">
+      <c r="G59" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="39.6">
       <c r="A60" s="3">
         <v>57</v>
       </c>
@@ -2760,7 +2761,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="171.6">
+    <row r="61" spans="1:8" ht="171.6">
       <c r="A61" s="3">
         <v>58</v>
       </c>
@@ -2781,7 +2782,7 @@
       </c>
       <c r="G61" s="6"/>
     </row>
-    <row r="62" spans="1:7" ht="52.8">
+    <row r="62" spans="1:8" ht="52.8">
       <c r="A62" s="3">
         <v>59</v>
       </c>
@@ -2972,18 +2973,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3005,25 +3006,25 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B34EA2C4-2285-4497-A663-7BC8A09FEAFD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B384905-33E6-4B60-BC29-CDB45CE8B04B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="8b8ad293-1655-4b1e-95cd-578b981aff66"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B384905-33E6-4B60-BC29-CDB45CE8B04B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B34EA2C4-2285-4497-A663-7BC8A09FEAFD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8b8ad293-1655-4b1e-95cd-578b981aff66"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/feedback-reports/Full-Stack_Development_with_GenAI_Honours_Program.xlsx
+++ b/feedback-reports/Full-Stack_Development_with_GenAI_Honours_Program.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30023"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nandita.vora\OneDrive - NIIT Limited\NIIT-AI Powered FSE - General\Design Docs\FSE-v6\Feedback-App\feedback-reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://niit.sharepoint.com/sites/NIIT-AIPoweredFSE/Shared Documents/General/Design Docs/FSE-v6/Website-Feedback/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="302" documentId="11_71F05A531246E64FEE670415535DCE3AA7C4B014" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{E88C2044-D968-4508-A85F-A5DA46ADCF1B}"/>
+  <xr:revisionPtr revIDLastSave="304" documentId="11_71F05A531246E64FEE670415535DCE3AA7C4B014" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{681F91B6-5588-4729-88BB-2E181085AEBE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,19 +16,30 @@
     <sheet name="Validation Report" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Validation Report'!$A$1:$F$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Validation Report'!$A$1:$F$61</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="179">
   <si>
     <t>Program Name</t>
   </si>
@@ -126,7 +137,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Replace with:
 </t>
@@ -137,7 +147,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve">• SQL Querying &amp; Data Operations
 </t>
@@ -147,7 +156,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Build strong hands-on skills to retrieve, analyze, and manipulate data using SQL, enabling you to extract meaningful insights and work effectively with real-world datasets.
 </t>
@@ -158,7 +166,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve">• Database Design, Integrity &amp; Advanced Capabilities
 </t>
@@ -168,7 +175,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>Design structured databases using ER diagrams and define robust schemas while ensuring data consistency, and extend functionality through automation and support for modern data formats.</t>
     </r>
@@ -222,7 +228,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Replace with : 
@@ -234,7 +239,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Core Java Programming &amp; Problem Solving
@@ -245,7 +249,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Apply Core Java fundamentals—variables, control flow, arrays, strings, recursion, and searching/sorting—to build efficient, program logic.
@@ -257,7 +260,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Object-Oriented Application Development
@@ -268,7 +270,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Apply object-oriented concepts and exception handling to design well-structured Java applications.</t>
@@ -331,7 +332,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Replace with :
@@ -343,7 +343,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">• Data Structures Implementation
@@ -354,7 +353,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Implement core data structures such as arrays, stacks, queues, linked lists, trees, and hash tables along with searching and sorting algorithms.
@@ -366,7 +364,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">• Algorithm Analysis and Optimization
@@ -377,7 +374,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Analyse time and space complexity and apply recursion and suitable data structures to solve performance-critical problems.</t>
@@ -449,7 +445,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Replace with 
@@ -461,7 +456,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Testing and Collections
@@ -472,7 +466,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Write unit tests and manage data using collections and generics for organized, reliable programs.
@@ -484,7 +477,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Modern Java Practices
@@ -495,7 +487,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Apply functional programming features to write concise, efficient code for data processing.</t>
@@ -552,7 +543,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Replace with:
@@ -564,7 +554,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Responsive Web Design &amp; User Experience
@@ -575,7 +564,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Create visually appealing and responsive web interfaces by structuring content effectively and applying modern styling practices aligned with UI/UX principles.
@@ -587,7 +575,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">• Interactive Web Development &amp; API Integration
@@ -598,7 +585,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Build dynamic, interactive web applications by handling user interactions and seamlessly connecting front-end interfaces with backend services through APIs.</t>
@@ -650,7 +636,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Replace with below:
@@ -662,7 +647,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Component-Based UI Development
@@ -673,7 +657,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Build reusable and maintainable user interfaces using JSX, components, and props.
@@ -685,7 +668,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">State, Interactivity &amp; Data Handling
@@ -696,7 +678,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Create dynamic apps by managing state, handling interactions, and integrating APIs with React hooks.
@@ -708,7 +689,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">• Scalable, Styled &amp; Tested Apps
@@ -719,7 +699,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Improve reliability with TypeScript, design responsive UIs using Material UI, and ensure quality through testing using Jest and RTL.</t>
@@ -729,7 +708,76 @@
     <t>Course 6 - Activity label</t>
   </si>
   <si>
-    <t>Course 6 - Activity options</t>
+    <t>Course 7 - Duration (weeks)</t>
+  </si>
+  <si>
+    <t>Weeks 21–23</t>
+  </si>
+  <si>
+    <t>Update to: 'Weeks 21–24'</t>
+  </si>
+  <si>
+    <t>Course 7 - Duration (hours)</t>
+  </si>
+  <si>
+    <t>Course 7 - Two-bullet course summary</t>
+  </si>
+  <si>
+    <t>1) Advanced React Application Development — Build complex, form-driven SPAs with React, including dynamic routing and secure role-based authentication. 2) Scalable State Management &amp; Optimization — Use reducers and context for efficient state management and develop optimized, production-ready applications.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">Replace with below content:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">• Forms &amp; Navigation in React Applications
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">Build and validate complex forms and enable seamless user journeys through efficient form handling and in-app routing.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">• Authentication, State Management &amp; Performance
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>Implement secure access control and manage application state effectively using Context API while optimizing performance for production-ready apps.</t>
+    </r>
+  </si>
+  <si>
+    <t>Course 7 - Activity label</t>
+  </si>
+  <si>
+    <t>Course  7- Activity options</t>
   </si>
   <si>
     <t xml:space="preserve">Bake My Cake – Digital catalog for cakes, cookies, and brownies, BookBuddy – Campus bookstore web app, DailyDash Lite – Habit &amp; mood heatmap tracker, Dairy Delights – Organic dairy product catalog
@@ -740,83 +788,6 @@
 TaskTrackr — Smart To-Do Dashboard</t>
   </si>
   <si>
-    <t>Course 7 - Duration (weeks)</t>
-  </si>
-  <si>
-    <t>Weeks 21–23</t>
-  </si>
-  <si>
-    <t>Update to: 'Weeks 21–24'</t>
-  </si>
-  <si>
-    <t>Course 7 - Duration (hours)</t>
-  </si>
-  <si>
-    <t>Course 7 - Two-bullet course summary</t>
-  </si>
-  <si>
-    <t>1) Advanced React Application Development — Build complex, form-driven SPAs with React, including dynamic routing and secure role-based authentication. 2) Scalable State Management &amp; Optimization — Use reducers and context for efficient state management and develop optimized, production-ready applications.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Replace with below content:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">• Forms &amp; Navigation in React Applications
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Build and validate complex forms and enable seamless user journeys through efficient form handling and in-app routing.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">• Authentication, State Management &amp; Performance
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Implement secure access control and manage application state effectively using Context API while optimizing performance for production-ready apps.</t>
-    </r>
-  </si>
-  <si>
-    <t>Course 7 - Activity label</t>
-  </si>
-  <si>
-    <t>Course  7- Activity options</t>
-  </si>
-  <si>
     <t>Course 8 - Title</t>
   </si>
   <si>
@@ -845,7 +816,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">API Development and Testing
@@ -856,7 +826,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Design, build, and test RESTful APIs using Spring Boot with relational and NoSQL databases, including documentation and performance validation.
@@ -868,7 +837,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Scalability and Security
@@ -879,7 +847,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Enhance and secure services with pagination, filtering, microservices architecture, and authentication mechanisms.</t>
@@ -942,7 +909,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">LLM Application Development
@@ -953,7 +919,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Build LLM-powered applications using Spring AI with text generation, prompt design, and structured outputs.
@@ -965,7 +930,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Context-Aware AI Systems
@@ -976,7 +940,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Enhance applications with conversational memory and Retrieval-Augmented Generation (RAG) for context-driven experiences.</t>
@@ -1073,24 +1036,12 @@
   <si>
     <t>Replace with: 'Build and integrate AI features into full-stack web applications using Spring AI, including conversational memory and Retrieval-Augmented Generation (RAG).'</t>
   </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>suggestion fixed</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1103,7 +1054,6 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1115,26 +1065,22 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1142,7 +1088,6 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1164,7 +1109,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1182,20 +1126,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1219,14 +1151,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F3864"/>
-        <bgColor rgb="FF1F3864"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1249,23 +1175,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1305,15 +1220,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1623,18 +1529,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H62"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8"/>
+  <dimension ref="A1:H63"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="19" style="2" customWidth="1"/>
-    <col min="2" max="2" width="83.6640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="83.7109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="25" style="2" customWidth="1"/>
     <col min="4" max="4" width="45" style="2" customWidth="1"/>
     <col min="5" max="5" width="40" style="2" customWidth="1"/>
     <col min="6" max="6" width="45" style="2" customWidth="1"/>
-    <col min="7" max="7" width="46.5546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="36.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.109375" style="2"/>
+    <col min="7" max="7" width="46.5703125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="36.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" ht="24" customHeight="1">
@@ -1648,13 +1554,11 @@
         <v>2</v>
       </c>
       <c r="D1" s="9">
-        <f>COUNTA(A4:A62)</f>
-        <v>59</v>
+        <f>COUNTA(A4:A61)</f>
+        <v>58</v>
       </c>
       <c r="E1" s="12"/>
       <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" s="10" customFormat="1" ht="30.75" customHeight="1">
       <c r="A2" s="9" t="s">
@@ -1667,8 +1571,6 @@
       <c r="D2" s="9"/>
       <c r="E2" s="12"/>
       <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
@@ -1689,14 +1591,8 @@
       <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="52.8">
+    </row>
+    <row r="4" spans="1:8" ht="48">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -1713,10 +1609,10 @@
       <c r="F4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-    </row>
-    <row r="5" spans="1:8" ht="26.4">
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" spans="1:8" ht="24">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -1734,7 +1630,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="52.8">
+    <row r="6" spans="1:8" ht="48">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -1754,7 +1650,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="39.6">
+    <row r="7" spans="1:8" ht="24">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -1774,7 +1670,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="184.8">
+    <row r="8" spans="1:8" ht="154.5">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -1792,7 +1688,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" ht="12.75">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -1810,7 +1706,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="66">
+    <row r="10" spans="1:8" ht="60">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -1828,7 +1724,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" ht="12.75">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -1846,7 +1742,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="39.6">
+    <row r="12" spans="1:8" ht="24">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -1866,7 +1762,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="124.2">
+    <row r="13" spans="1:8" ht="121.5">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -1884,7 +1780,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" ht="12.75">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -1902,7 +1798,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="132">
+    <row r="15" spans="1:8" ht="118.5">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -1922,7 +1818,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="39.6">
+    <row r="16" spans="1:8" ht="36">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -1942,7 +1838,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" ht="12.75">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -1960,7 +1856,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" ht="12.75">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -1978,7 +1874,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="138">
+    <row r="19" spans="1:6" ht="135">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -1996,7 +1892,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" ht="12.75">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -2014,7 +1910,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="26.4">
+    <row r="21" spans="1:6" ht="24">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -2034,7 +1930,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="79.2">
+    <row r="22" spans="1:6" ht="72">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -2054,7 +1950,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="39.6">
+    <row r="23" spans="1:6" ht="36">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -2074,7 +1970,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" ht="12.75">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -2092,7 +1988,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" ht="12.75">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -2110,7 +2006,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="110.4">
+    <row r="26" spans="1:6" ht="108">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -2128,7 +2024,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" ht="12.75">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -2146,7 +2042,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="52.8">
+    <row r="28" spans="1:6" ht="48">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -2166,7 +2062,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="132">
+    <row r="29" spans="1:6" ht="118.5">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -2186,7 +2082,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="26.4">
+    <row r="30" spans="1:6" ht="24">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -2206,7 +2102,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" ht="12.75">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -2224,7 +2120,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="124.2">
+    <row r="32" spans="1:6" ht="121.5">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -2242,7 +2138,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" ht="12.75">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -2260,7 +2156,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="79.2">
+    <row r="34" spans="1:8" ht="72">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -2278,7 +2174,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="27.6">
+    <row r="35" spans="1:8" ht="13.5">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -2298,7 +2194,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" ht="12.75">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -2316,7 +2212,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" ht="13.5">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -2335,7 +2231,7 @@
       </c>
       <c r="H37" s="8"/>
     </row>
-    <row r="38" spans="1:8" ht="179.4">
+    <row r="38" spans="1:8" ht="174.75">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -2353,7 +2249,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" ht="12.75">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -2371,25 +2267,25 @@
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="79.2">
+    <row r="40" spans="1:8" ht="12.75">
       <c r="A40" s="3">
         <v>37</v>
       </c>
-      <c r="B40" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C40" s="13" t="s">
+      <c r="B40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13" t="s">
+      <c r="E40" s="3"/>
+      <c r="F40" s="3" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" ht="12.75">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -2400,14 +2296,14 @@
         <v>119</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="118.5">
       <c r="A42" s="3">
         <v>39</v>
       </c>
@@ -2415,17 +2311,17 @@
         <v>19</v>
       </c>
       <c r="C42" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E42" s="3"/>
+      <c r="F42" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="145.19999999999999">
+    </row>
+    <row r="43" spans="1:8" ht="12.75">
       <c r="A43" s="3">
         <v>40</v>
       </c>
@@ -2436,50 +2332,50 @@
         <v>123</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>124</v>
+        <v>32</v>
       </c>
       <c r="E43" s="3"/>
-      <c r="F43" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+      <c r="F43" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="72">
       <c r="A44" s="3">
         <v>41</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C44" s="3" t="s">
+      <c r="B44" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="79.2">
+    </row>
+    <row r="45" spans="1:8" ht="24">
       <c r="A45" s="3">
         <v>42</v>
       </c>
-      <c r="B45" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C45" s="13" t="s">
+      <c r="B45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D45" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="26.4">
+      <c r="D45" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="12.75">
       <c r="A46" s="3">
         <v>43</v>
       </c>
@@ -2487,17 +2383,17 @@
         <v>19</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="135">
       <c r="A47" s="3">
         <v>44</v>
       </c>
@@ -2508,14 +2404,14 @@
         <v>131</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="E47" s="3"/>
-      <c r="F47" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="138">
+      <c r="F47" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="12.75">
       <c r="A48" s="3">
         <v>45</v>
       </c>
@@ -2523,53 +2419,55 @@
         <v>19</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>133</v>
+        <v>32</v>
       </c>
       <c r="E48" s="3"/>
-      <c r="F48" s="5" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="F48" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="72">
       <c r="A49" s="3">
         <v>46</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C49" s="3" t="s">
+      <c r="B49" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="79.2">
+      <c r="D49" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="24">
       <c r="A50" s="3">
         <v>47</v>
       </c>
-      <c r="B50" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13" t="s">
+      <c r="B50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" ht="26.4">
+      <c r="D50" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="12.75">
       <c r="A51" s="3">
         <v>48</v>
       </c>
@@ -2577,19 +2475,17 @@
         <v>19</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>95</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="E51" s="3"/>
       <c r="F51" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="12.75">
       <c r="A52" s="3">
         <v>49</v>
       </c>
@@ -2597,17 +2493,17 @@
         <v>19</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="121.5">
       <c r="A53" s="3">
         <v>50</v>
       </c>
@@ -2615,17 +2511,17 @@
         <v>19</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E53" s="3"/>
-      <c r="F53" s="3" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="138">
+      <c r="F53" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="12.75">
       <c r="A54" s="3">
         <v>51</v>
       </c>
@@ -2633,17 +2529,17 @@
         <v>19</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="E54" s="3"/>
-      <c r="F54" s="5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
+      <c r="F54" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="84">
       <c r="A55" s="3">
         <v>52</v>
       </c>
@@ -2654,14 +2550,14 @@
         <v>151</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>32</v>
+        <v>152</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="92.4">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="60">
       <c r="A56" s="3">
         <v>53</v>
       </c>
@@ -2669,140 +2565,119 @@
         <v>19</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E56" s="3"/>
+        <v>155</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>156</v>
+      </c>
       <c r="F56" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="66">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="48">
       <c r="A57" s="3">
         <v>54</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>19</v>
+        <v>158</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>157</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="52.8">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="24">
       <c r="A58" s="3">
         <v>55</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="E58" s="3"/>
+        <v>164</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>165</v>
+      </c>
       <c r="F58" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="39.6">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="36">
       <c r="A59" s="3">
         <v>56</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>166</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="39.6">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="142.5">
       <c r="A60" s="3">
         <v>57</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E60" s="3"/>
+        <v>172</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>173</v>
+      </c>
       <c r="F60" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="171.6">
+        <v>174</v>
+      </c>
+      <c r="G60" s="6"/>
+    </row>
+    <row r="61" spans="1:7" ht="48">
       <c r="A61" s="3">
         <v>58</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="G61" s="6"/>
-    </row>
-    <row r="62" spans="1:8" ht="52.8">
-      <c r="A62" s="3">
-        <v>59</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E62" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
+    </row>
+    <row r="62" spans="1:7" ht="12.75"/>
+    <row r="63" spans="1:7" ht="12.75"/>
   </sheetData>
+  <autoFilter ref="A1:F61" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{7EC993AE-BD08-4FAE-B116-D47C25032B82}"/>
   </hyperlinks>
@@ -2973,6 +2848,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -2981,50 +2862,14 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A0A7D80-6346-4EAB-865F-2A3CADAA0676}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="8b8ad293-1655-4b1e-95cd-578b981aff66"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A0A7D80-6346-4EAB-865F-2A3CADAA0676}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B384905-33E6-4B60-BC29-CDB45CE8B04B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B34EA2C4-2285-4497-A663-7BC8A09FEAFD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B34EA2C4-2285-4497-A663-7BC8A09FEAFD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="8b8ad293-1655-4b1e-95cd-578b981aff66"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B384905-33E6-4B60-BC29-CDB45CE8B04B}"/>
 </file>